--- a/data/trans_dic/P36$otros-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,23</t>
+          <t>1,36; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,69</t>
+          <t>0,61; 3,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,67</t>
+          <t>1,11; 5,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,93</t>
+          <t>0,41; 3,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,33; 2,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,98</t>
+          <t>1,7; 5,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,51</t>
+          <t>1,12; 3,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,63</t>
+          <t>0,64; 2,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,85</t>
+          <t>1,91; 4,87</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,48</t>
+          <t>1,47; 4,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,12</t>
+          <t>0,47; 3,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,17</t>
+          <t>0,77; 3,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,7</t>
+          <t>0,19; 1,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,35</t>
+          <t>1,36; 3,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,18</t>
+          <t>0,09; 1,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,93</t>
+          <t>0,49; 1,98</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,46</t>
+          <t>0,27; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,97</t>
+          <t>0,3; 2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,75</t>
+          <t>0,65; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,48</t>
+          <t>1,16; 4,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,38</t>
+          <t>0,61; 2,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,01</t>
+          <t>0,91; 3,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,99</t>
+          <t>0,14; 1,91</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,8</t>
+          <t>1,47; 5,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,53</t>
+          <t>0,86; 4,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,26; 29,69</t>
+          <t>19,49; 29,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,99</t>
+          <t>1,59; 4,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,5</t>
+          <t>0,23; 2,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,61; 29,25</t>
+          <t>19,71; 28,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,46</t>
+          <t>1,87; 4,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,01</t>
+          <t>0,82; 2,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 27,75</t>
+          <t>21,61; 27,96</t>
         </is>
       </c>
     </row>
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,56</t>
+          <t>1,43; 5,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,86</t>
+          <t>0,34; 3,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,38</t>
+          <t>0,37; 3,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,57</t>
+          <t>0,18; 1,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,78</t>
+          <t>0,34; 1,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,51</t>
+          <t>1,13; 3,66</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,87</t>
+          <t>0,63; 2,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,36</t>
+          <t>0,95; 3,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,68</t>
+          <t>1,93; 4,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,63</t>
+          <t>1,25; 3,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,66</t>
+          <t>1,18; 3,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,91</t>
+          <t>2,82; 5,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,77</t>
+          <t>1,18; 2,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,18</t>
+          <t>1,38; 3,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,83</t>
+          <t>2,56; 4,72</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,95</t>
+          <t>1,06; 3,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,48</t>
+          <t>0,79; 2,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,45</t>
+          <t>0,24; 1,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,19</t>
+          <t>0,13; 1,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,38</t>
+          <t>1,07; 2,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,86</t>
+          <t>0,13; 0,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,8</t>
+          <t>0,13; 0,79</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,33</t>
+          <t>1,42; 2,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,55</t>
+          <t>0,76; 1,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,77</t>
+          <t>3,35; 4,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,09</t>
+          <t>1,26; 2,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,54</t>
+          <t>0,82; 1,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,84</t>
+          <t>3,51; 4,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,08</t>
+          <t>1,41; 2,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,38</t>
+          <t>0,86; 1,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,61</t>
+          <t>3,62; 4,6</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3682; 14198</t>
+          <t>3698; 14260</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1744; 10878</t>
+          <t>1785; 10466</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3898; 16651</t>
+          <t>3252; 15498</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1052; 10221</t>
+          <t>1054; 9273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 8336</t>
+          <t>935; 8409</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5472; 17260</t>
+          <t>4896; 17110</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5785; 18632</t>
+          <t>5926; 19908</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3553; 15269</t>
+          <t>3699; 15618</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10839; 28258</t>
+          <t>11111; 28349</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7137; 22029</t>
+          <t>7222; 21941</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 12047</t>
+          <t>0; 12888</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2908; 15597</t>
+          <t>2332; 15387</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3116; 15989</t>
+          <t>3898; 15587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6026</t>
+          <t>0; 5983</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>981; 8880</t>
+          <t>984; 9248</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13910; 33378</t>
+          <t>13496; 33032</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>899; 12143</t>
+          <t>889; 12025</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5180; 19772</t>
+          <t>4988; 20247</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>870; 7828</t>
+          <t>875; 8495</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>959; 9604</t>
+          <t>954; 9562</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4820</t>
+          <t>0; 4810</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2718; 12578</t>
+          <t>2190; 12448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3893; 15274</t>
+          <t>3962; 15213</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 11069</t>
+          <t>0; 10986</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3924; 15571</t>
+          <t>4001; 17595</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6829; 20007</t>
+          <t>6044; 19964</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>925; 13009</t>
+          <t>921; 12482</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5455; 20760</t>
+          <t>5259; 19445</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3260; 16905</t>
+          <t>3191; 16263</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74953; 109836</t>
+          <t>72121; 108220</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5492; 18546</t>
+          <t>5903; 17798</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>990; 9738</t>
+          <t>907; 8908</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75948; 113284</t>
+          <t>76322; 110730</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13775; 32489</t>
+          <t>13637; 32136</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6452; 22962</t>
+          <t>6228; 22564</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>160659; 210149</t>
+          <t>163624; 211705</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5212</t>
+          <t>0; 4670</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1903</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4439</t>
+          <t>0; 4520</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4664</t>
+          <t>0; 4670</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>0; 4993</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1893</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4965</t>
+          <t>0; 5004</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6812</t>
+          <t>0; 6537</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3770; 14620</t>
+          <t>3756; 14468</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7807</t>
+          <t>0; 7267</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>951; 7993</t>
+          <t>950; 8831</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>999; 9183</t>
+          <t>1000; 9232</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>987; 8612</t>
+          <t>989; 9757</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1784; 9863</t>
+          <t>1884; 10759</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6135; 18774</t>
+          <t>6063; 19594</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4146; 17609</t>
+          <t>3832; 18056</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6844; 22247</t>
+          <t>6325; 22271</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11249; 30638</t>
+          <t>12615; 30291</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7209; 23117</t>
+          <t>7962; 23688</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8255; 25414</t>
+          <t>8164; 27031</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18820; 40719</t>
+          <t>19445; 39849</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14859; 34645</t>
+          <t>14746; 33576</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18602; 43185</t>
+          <t>18769; 42921</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35471; 64852</t>
+          <t>34373; 63376</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7783; 21950</t>
+          <t>7866; 22363</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5183</t>
+          <t>0; 6141</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 7430</t>
+          <t>0; 6096</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6025; 19410</t>
+          <t>6177; 19947</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2001; 11878</t>
+          <t>1998; 11039</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1051; 9862</t>
+          <t>1108; 10243</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16858; 36290</t>
+          <t>16337; 35741</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2178; 13809</t>
+          <t>2069; 13407</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2142; 12782</t>
+          <t>2065; 12624</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>46143; 76136</t>
+          <t>46331; 77733</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24101; 52927</t>
+          <t>25950; 51016</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>114086; 161648</t>
+          <t>113648; 162985</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41555; 70627</t>
+          <t>42427; 71113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>29013; 54551</t>
+          <t>29090; 56910</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>125167; 171338</t>
+          <t>124407; 171662</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96628; 138150</t>
+          <t>93955; 138486</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>61548; 96497</t>
+          <t>59747; 95957</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>251277; 319791</t>
+          <t>251000; 318902</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$otros-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,26</t>
+          <t>1,06; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,55</t>
+          <t>0,57; 3,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,28</t>
+          <t>1,09; 5,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,57</t>
+          <t>0,39; 3,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,94</t>
+          <t>0,33; 2,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,93</t>
+          <t>1,76; 5,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,75</t>
+          <t>1,1; 3,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,69</t>
+          <t>0,53; 2,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,87</t>
+          <t>1,87; 4,79</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,46</t>
+          <t>1,49; 4,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,07</t>
+          <t>0,6; 3,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,09</t>
+          <t>0,76; 3,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,77</t>
+          <t>0,19; 1,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,32</t>
+          <t>1,4; 3,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,17</t>
+          <t>0,09; 1,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,98</t>
+          <t>0,52; 2,02</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,66</t>
+          <t>0,27; 2,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,96</t>
+          <t>0,29; 2,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,71</t>
+          <t>0,67; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,46</t>
+          <t>1,16; 4,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,69</t>
+          <t>0,71; 2,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,01</t>
+          <t>1,03; 2,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,91</t>
+          <t>0,14; 1,8</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,44</t>
+          <t>1,35; 5,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,36</t>
+          <t>1,1; 4,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,49; 29,25</t>
+          <t>20,49; 29,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,79</t>
+          <t>1,47; 4,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,29</t>
+          <t>0,25; 2,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,71; 28,59</t>
+          <t>20,02; 29,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,41</t>
+          <t>1,76; 4,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,96</t>
+          <t>0,78; 2,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,61; 27,96</t>
+          <t>21,39; 27,72</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,5</t>
+          <t>1,47; 5,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,17</t>
+          <t>0,34; 2,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,4</t>
+          <t>0,37; 3,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,78</t>
+          <t>0,18; 1,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,95</t>
+          <t>0,34; 1,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,66</t>
+          <t>1,11; 3,66</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,95</t>
+          <t>0,71; 3,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,36</t>
+          <t>1,03; 3,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,63</t>
+          <t>1,81; 4,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,72</t>
+          <t>1,19; 3,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,9</t>
+          <t>1,18; 3,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,78</t>
+          <t>2,86; 5,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,69</t>
+          <t>1,13; 2,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,16</t>
+          <t>1,34; 3,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,72</t>
+          <t>2,73; 4,81</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,01</t>
+          <t>1,09; 3,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,55</t>
+          <t>0,8; 2,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,34</t>
+          <t>0,24; 1,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,24</t>
+          <t>0,13; 1,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,34</t>
+          <t>1,15; 2,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,84</t>
+          <t>0,14; 0,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,79</t>
+          <t>0,14; 0,78</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,38</t>
+          <t>1,36; 2,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,49</t>
+          <t>0,74; 1,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,81</t>
+          <t>3,38; 4,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,11</t>
+          <t>1,26; 2,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,6</t>
+          <t>0,82; 1,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,85</t>
+          <t>3,56; 4,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,08</t>
+          <t>1,4; 2,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,38</t>
+          <t>0,88; 1,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,6</t>
+          <t>3,59; 4,62</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3698; 14260</t>
+          <t>2862; 13330</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1785; 10466</t>
+          <t>1690; 10470</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3252; 15498</t>
+          <t>3187; 16690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1054; 9273</t>
+          <t>1021; 9725</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>935; 8409</t>
+          <t>938; 8516</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4896; 17110</t>
+          <t>5073; 17171</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5926; 19908</t>
+          <t>5848; 19326</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3699; 15618</t>
+          <t>3073; 14666</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11111; 28349</t>
+          <t>10874; 27875</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7222; 21941</t>
+          <t>7316; 21905</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 12888</t>
+          <t>0; 10656</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2332; 15387</t>
+          <t>3003; 15894</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3898; 15587</t>
+          <t>3822; 15507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5983</t>
+          <t>0; 5205</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>984; 9248</t>
+          <t>976; 8537</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13496; 33032</t>
+          <t>13924; 32375</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>889; 12025</t>
+          <t>895; 13667</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4988; 20247</t>
+          <t>5284; 20723</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>875; 8495</t>
+          <t>868; 8108</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>954; 9562</t>
+          <t>940; 9042</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4810</t>
+          <t>0; 4892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2190; 12448</t>
+          <t>2236; 12159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3962; 15213</t>
+          <t>3944; 15973</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 10986</t>
+          <t>0; 11870</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4001; 17595</t>
+          <t>4625; 15817</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6044; 19964</t>
+          <t>6859; 18986</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>921; 12482</t>
+          <t>926; 11782</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5259; 19445</t>
+          <t>4817; 19084</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3191; 16263</t>
+          <t>4099; 18314</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72121; 108220</t>
+          <t>75797; 109629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5903; 17798</t>
+          <t>5464; 17387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>907; 8908</t>
+          <t>981; 9631</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76322; 110730</t>
+          <t>77524; 113211</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13637; 32136</t>
+          <t>12812; 31394</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6228; 22564</t>
+          <t>5963; 22184</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>163624; 211705</t>
+          <t>161950; 209884</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4670</t>
+          <t>0; 4651</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4520</t>
+          <t>0; 4560</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4670</t>
+          <t>0; 4847</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4993</t>
+          <t>0; 4597</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 4963</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6537</t>
+          <t>0; 7186</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3756; 14468</t>
+          <t>3877; 14507</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7267</t>
+          <t>0; 8016</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>950; 8831</t>
+          <t>946; 7990</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1000; 9232</t>
+          <t>1001; 9967</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>989; 9757</t>
+          <t>984; 8658</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1884; 10759</t>
+          <t>1882; 10548</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6063; 19594</t>
+          <t>5922; 19603</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3832; 18056</t>
+          <t>4380; 19381</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6325; 22271</t>
+          <t>6812; 22532</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12615; 30291</t>
+          <t>11846; 30224</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7962; 23688</t>
+          <t>7571; 21601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8164; 27031</t>
+          <t>8203; 25902</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19445; 39849</t>
+          <t>19706; 41032</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14746; 33576</t>
+          <t>14135; 33633</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18769; 42921</t>
+          <t>18239; 42755</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>34373; 63376</t>
+          <t>36740; 64600</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7866; 22363</t>
+          <t>8077; 24404</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6141</t>
+          <t>0; 5175</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6096</t>
+          <t>0; 6677</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6177; 19947</t>
+          <t>6294; 20043</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1998; 11039</t>
+          <t>2011; 11598</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1108; 10243</t>
+          <t>1076; 9734</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16337; 35741</t>
+          <t>17568; 37040</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2069; 13407</t>
+          <t>2174; 12366</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2065; 12624</t>
+          <t>2208; 12452</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>46331; 77733</t>
+          <t>44323; 76151</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>25950; 51016</t>
+          <t>25315; 50568</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113648; 162985</t>
+          <t>114546; 164189</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42427; 71113</t>
+          <t>42586; 71838</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>29090; 56910</t>
+          <t>29161; 54949</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>124407; 171662</t>
+          <t>126126; 175735</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93955; 138486</t>
+          <t>93219; 136291</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>59747; 95957</t>
+          <t>61139; 95274</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>251000; 318902</t>
+          <t>248685; 320337</t>
         </is>
       </c>
     </row>
